--- a/course_data/salary_data_scrambled.xlsx
+++ b/course_data/salary_data_scrambled.xlsx
@@ -1,410 +1,418 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lauriercloud-my.sharepoint.com/personal/skiss_wlu_ca/Documents/Courses/RLISPOP/course_data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_E8829338EDF1A1E8B2443A4E5FC10EB7FEDB5D58" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8484542-CFC8-EE48-8744-1B0D4E876B99}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="2420" yWindow="2260" windowWidth="35980" windowHeight="17840" xr2:uid="{5E2D9560-8DE3-564E-8FE6-9C203AE28932}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="131">
-  <si>
-    <t xml:space="preserve">Timestamp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How old are you?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What industry do you work in?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What is your annual salary? (You'll indicate the currency in a later question. If you are part-time or hourly, please enter an annualized equivalent -- what you would earn if you worked the job 40 hours a week, 52 weeks a year.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Please indicate the currency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What country do you work in?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">If you're in the U.S., what state do you work in?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How many years of professional work experience do you have overall?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What is your highest level of education completed?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What is your gender?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What is your race? (Choose all that apply.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Education (Higher Education)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massachusetts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5-7 years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Master's degree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Woman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">White</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computing or Tech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">,GBP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United Kingdom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 - 10 years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">College degree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-binary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accounting, Banking &amp; Finance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tennessee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 4 years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">,25-34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nonprofits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@62000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wisconsin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Carolina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New Hampshire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Man</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Publishing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Education (Primary/Secondary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arizona</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45-54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Missouri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 - 30 years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Florida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hispanic, Latino, or Spanish origin, White</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pennsylvania</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 - 20 years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PhD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michigan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asian or Asian American, White</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Law</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minnesota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 year or less</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utilities &amp; Telecommunications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GBP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business or Consulting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Illinois</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Some college</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Art &amp; Design</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">usa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">California</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Georgia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Health care</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;5-7 years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@Master's degree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Government and Public Administration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ohio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asian or Asian American</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public Library</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;Michigan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">District of Columbia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maryland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Another option not listed here or prefer not to answer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;Government and Public Administration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering or Manufacturing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Texas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Media &amp; Digital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">,USA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">230000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virginia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North Carolina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New York</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@Woman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marketing, Advertising &amp; PR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200850</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@White</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="131">
+  <si>
+    <t>Timestamp</t>
+  </si>
+  <si>
+    <t>How old are you?</t>
+  </si>
+  <si>
+    <t>What industry do you work in?</t>
+  </si>
+  <si>
+    <t>What is your annual salary? (You'll indicate the currency in a later question. If you are part-time or hourly, please enter an annualized equivalent -- what you would earn if you worked the job 40 hours a week, 52 weeks a year.)</t>
+  </si>
+  <si>
+    <t>Please indicate the currency</t>
+  </si>
+  <si>
+    <t>What country do you work in?</t>
+  </si>
+  <si>
+    <t>If you're in the U.S., what state do you work in?</t>
+  </si>
+  <si>
+    <t>How many years of professional work experience do you have overall?</t>
+  </si>
+  <si>
+    <t>What is your highest level of education completed?</t>
+  </si>
+  <si>
+    <t>What is your gender?</t>
+  </si>
+  <si>
+    <t>What is your race? (Choose all that apply.)</t>
+  </si>
+  <si>
+    <t>25-34</t>
+  </si>
+  <si>
+    <t>Education (Higher Education)</t>
+  </si>
+  <si>
+    <t>55000</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
+    <t>Massachusetts</t>
+  </si>
+  <si>
+    <t>5-7 years</t>
+  </si>
+  <si>
+    <t>Master's degree</t>
+  </si>
+  <si>
+    <t>Woman</t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>Computing or Tech</t>
+  </si>
+  <si>
+    <t>54600</t>
+  </si>
+  <si>
+    <t>,GBP</t>
+  </si>
+  <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
+    <t>8 - 10 years</t>
+  </si>
+  <si>
+    <t>College degree</t>
+  </si>
+  <si>
+    <t>Non-binary</t>
+  </si>
+  <si>
+    <t>Accounting, Banking &amp; Finance</t>
+  </si>
+  <si>
+    <t>34000</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>Tennessee</t>
+  </si>
+  <si>
+    <t>2 - 4 years</t>
+  </si>
+  <si>
+    <t>,25-34</t>
+  </si>
+  <si>
+    <t>Nonprofits</t>
+  </si>
+  <si>
+    <t>@62000</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>Wisconsin</t>
+  </si>
+  <si>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>South Carolina</t>
+  </si>
+  <si>
+    <t>62000</t>
+  </si>
+  <si>
+    <t>New Hampshire</t>
+  </si>
+  <si>
+    <t>Man</t>
+  </si>
+  <si>
+    <t>Publishing</t>
+  </si>
+  <si>
+    <t>Education (Primary/Secondary)</t>
+  </si>
+  <si>
+    <t>50000</t>
+  </si>
+  <si>
+    <t>Arizona</t>
+  </si>
+  <si>
+    <t>45-54</t>
+  </si>
+  <si>
+    <t>112000</t>
+  </si>
+  <si>
+    <t>Missouri</t>
+  </si>
+  <si>
+    <t>21 - 30 years</t>
+  </si>
+  <si>
+    <t>35-44</t>
+  </si>
+  <si>
+    <t>45000</t>
+  </si>
+  <si>
+    <t>Florida</t>
+  </si>
+  <si>
+    <t>Hispanic, Latino, or Spanish origin, White</t>
+  </si>
+  <si>
+    <t>47500</t>
+  </si>
+  <si>
+    <t>Pennsylvania</t>
+  </si>
+  <si>
+    <t>11 - 20 years</t>
+  </si>
+  <si>
+    <t>PhD</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>Michigan</t>
+  </si>
+  <si>
+    <t>Asian or Asian American, White</t>
+  </si>
+  <si>
+    <t>Law</t>
+  </si>
+  <si>
+    <t>52000</t>
+  </si>
+  <si>
+    <t>Minnesota</t>
+  </si>
+  <si>
+    <t>18-24</t>
+  </si>
+  <si>
+    <t>32000</t>
+  </si>
+  <si>
+    <t>CAD</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>1 year or less</t>
+  </si>
+  <si>
+    <t>Utilities &amp; Telecommunications</t>
+  </si>
+  <si>
+    <t>24000</t>
+  </si>
+  <si>
+    <t>GBP</t>
+  </si>
+  <si>
+    <t>Business or Consulting</t>
+  </si>
+  <si>
+    <t>85000</t>
+  </si>
+  <si>
+    <t>Illinois</t>
+  </si>
+  <si>
+    <t>Some college</t>
+  </si>
+  <si>
+    <t>Art &amp; Design</t>
+  </si>
+  <si>
+    <t>59000</t>
+  </si>
+  <si>
+    <t>usa</t>
+  </si>
+  <si>
+    <t>California</t>
+  </si>
+  <si>
+    <t>98000</t>
+  </si>
+  <si>
+    <t>Georgia</t>
+  </si>
+  <si>
+    <t>54000</t>
+  </si>
+  <si>
+    <t>Health care</t>
+  </si>
+  <si>
+    <t>74000</t>
+  </si>
+  <si>
+    <t>&amp;5-7 years</t>
+  </si>
+  <si>
+    <t>63000</t>
+  </si>
+  <si>
+    <t>@Master's degree</t>
+  </si>
+  <si>
+    <t>Government and Public Administration</t>
+  </si>
+  <si>
+    <t>96000</t>
+  </si>
+  <si>
+    <t>Ohio</t>
+  </si>
+  <si>
+    <t>Asian or Asian American</t>
+  </si>
+  <si>
+    <t>Public Library</t>
+  </si>
+  <si>
+    <t>44500</t>
+  </si>
+  <si>
+    <t>&amp;Michigan</t>
+  </si>
+  <si>
+    <t>District of Columbia</t>
+  </si>
+  <si>
+    <t>48000</t>
+  </si>
+  <si>
+    <t>Maryland</t>
+  </si>
+  <si>
+    <t>Another option not listed here or prefer not to answer</t>
+  </si>
+  <si>
+    <t>&amp;Government and Public Administration</t>
+  </si>
+  <si>
+    <t>140000</t>
+  </si>
+  <si>
+    <t>Engineering or Manufacturing</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>Texas</t>
+  </si>
+  <si>
+    <t>39000</t>
+  </si>
+  <si>
+    <t>Media &amp; Digital</t>
+  </si>
+  <si>
+    <t>125000</t>
+  </si>
+  <si>
+    <t>,USA</t>
+  </si>
+  <si>
+    <t>230000</t>
+  </si>
+  <si>
+    <t>110000</t>
+  </si>
+  <si>
+    <t>Virginia</t>
+  </si>
+  <si>
+    <t>68000</t>
+  </si>
+  <si>
+    <t>North Carolina</t>
+  </si>
+  <si>
+    <t>41000</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>78000</t>
+  </si>
+  <si>
+    <t>@Woman</t>
+  </si>
+  <si>
+    <t>37,000</t>
+  </si>
+  <si>
+    <t>Marketing, Advertising &amp; PR</t>
+  </si>
+  <si>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>UK</t>
+  </si>
+  <si>
+    <t>65000</t>
+  </si>
+  <si>
+    <t>187500</t>
+  </si>
+  <si>
+    <t>66625</t>
+  </si>
+  <si>
+    <t>144600</t>
+  </si>
+  <si>
+    <t>200850</t>
+  </si>
+  <si>
+    <t>120000</t>
+  </si>
+  <si>
+    <t>Retail</t>
+  </si>
+  <si>
+    <t>97500</t>
+  </si>
+  <si>
+    <t>@White</t>
   </si>
 </sst>
 </file>
@@ -412,9 +420,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy/mm/dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -426,6 +434,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -450,13 +459,26 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -737,11 +759,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="36.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -776,9 +801,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>44313.4598349884</v>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>44313.459834988404</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
@@ -811,9 +836,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>44313.4599717824</v>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>44313.459971782402</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
@@ -830,7 +855,6 @@
       <c r="F3" t="s">
         <v>24</v>
       </c>
-      <c r="G3"/>
       <c r="H3" t="s">
         <v>25</v>
       </c>
@@ -844,9 +868,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>44313.4601634838</v>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>44313.460163483804</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
@@ -879,9 +903,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>44313.4601926273</v>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>44313.460192627303</v>
       </c>
       <c r="B5" t="s">
         <v>33</v>
@@ -914,9 +938,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>44313.4602059375</v>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>44313.460205937503</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
@@ -949,9 +973,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>44313.4602496643</v>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>44313.460249664298</v>
       </c>
       <c r="B7" t="s">
         <v>11</v>
@@ -962,7 +986,6 @@
       <c r="D7" t="s">
         <v>40</v>
       </c>
-      <c r="E7"/>
       <c r="F7" t="s">
         <v>36</v>
       </c>
@@ -982,9 +1005,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>44313.460306794</v>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>44313.460306793997</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
@@ -992,7 +1015,6 @@
       <c r="C8" t="s">
         <v>43</v>
       </c>
-      <c r="D8"/>
       <c r="E8" t="s">
         <v>14</v>
       </c>
@@ -1015,9 +1037,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>44313.4604158218</v>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>44313.460415821799</v>
       </c>
       <c r="B9" t="s">
         <v>11</v>
@@ -1050,9 +1072,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>44313.4604287616</v>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>44313.460428761602</v>
       </c>
       <c r="B10" t="s">
         <v>47</v>
@@ -1085,9 +1107,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>44313.460436331</v>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>44313.460436330999</v>
       </c>
       <c r="B11" t="s">
         <v>51</v>
@@ -1120,9 +1142,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>44313.46044875</v>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>44313.460448749996</v>
       </c>
       <c r="B12" t="s">
         <v>11</v>
@@ -1139,7 +1161,6 @@
       <c r="F12" t="s">
         <v>15</v>
       </c>
-      <c r="G12"/>
       <c r="H12" t="s">
         <v>17</v>
       </c>
@@ -1153,9 +1174,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>44313.4605006366</v>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>44313.460500636596</v>
       </c>
       <c r="B13" t="s">
         <v>51</v>
@@ -1188,9 +1209,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>44313.4605235648</v>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>44313.460523564798</v>
       </c>
       <c r="B14" t="s">
         <v>51</v>
@@ -1223,8 +1244,8 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
         <v>44313.4605291435</v>
       </c>
       <c r="B15" t="s">
@@ -1248,7 +1269,6 @@
       <c r="H15" t="s">
         <v>32</v>
       </c>
-      <c r="I15"/>
       <c r="J15" t="s">
         <v>19</v>
       </c>
@@ -1256,14 +1276,13 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>44313.4605389931</v>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>44313.460538993102</v>
       </c>
       <c r="B16" t="s">
         <v>65</v>
       </c>
-      <c r="C16"/>
       <c r="D16" t="s">
         <v>66</v>
       </c>
@@ -1273,7 +1292,6 @@
       <c r="F16" t="s">
         <v>68</v>
       </c>
-      <c r="G16"/>
       <c r="H16" t="s">
         <v>69</v>
       </c>
@@ -1287,9 +1305,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>44313.4605440972</v>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>44313.460544097201</v>
       </c>
       <c r="B17" t="s">
         <v>51</v>
@@ -1306,7 +1324,6 @@
       <c r="F17" t="s">
         <v>24</v>
       </c>
-      <c r="G17"/>
       <c r="H17" t="s">
         <v>57</v>
       </c>
@@ -1320,9 +1337,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>44313.4605718056</v>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>44313.460571805597</v>
       </c>
       <c r="B18" t="s">
         <v>51</v>
@@ -1348,14 +1365,13 @@
       <c r="I18" t="s">
         <v>76</v>
       </c>
-      <c r="J18"/>
       <c r="K18" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>44313.4606329514</v>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>44313.460632951399</v>
       </c>
       <c r="B19" t="s">
         <v>47</v>
@@ -1388,8 +1404,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
         <v>44313.4606563079</v>
       </c>
       <c r="B20" t="s">
@@ -1410,7 +1426,6 @@
       <c r="G20" t="s">
         <v>82</v>
       </c>
-      <c r="H20"/>
       <c r="I20" t="s">
         <v>18</v>
       </c>
@@ -1421,9 +1436,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>44313.4606836343</v>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>44313.460683634301</v>
       </c>
       <c r="B21" t="s">
         <v>51</v>
@@ -1456,8 +1471,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
         <v>44313.460692581</v>
       </c>
       <c r="B22" t="s">
@@ -1491,9 +1506,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>44313.4606975579</v>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>44313.460697557901</v>
       </c>
       <c r="B23" t="s">
         <v>51</v>
@@ -1510,7 +1525,6 @@
       <c r="F23" t="s">
         <v>15</v>
       </c>
-      <c r="G23"/>
       <c r="H23" t="s">
         <v>86</v>
       </c>
@@ -1524,9 +1538,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>44313.4607298032</v>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>44313.460729803199</v>
       </c>
       <c r="B24" t="s">
         <v>51</v>
@@ -1540,8 +1554,6 @@
       <c r="E24" t="s">
         <v>67</v>
       </c>
-      <c r="F24"/>
-      <c r="G24"/>
       <c r="H24" t="s">
         <v>57</v>
       </c>
@@ -1555,9 +1567,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>44313.4607515856</v>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>44313.460751585597</v>
       </c>
       <c r="B25" t="s">
         <v>51</v>
@@ -1590,8 +1602,8 @@
         <v>92</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
         <v>44313.460781169</v>
       </c>
       <c r="B26" t="s">
@@ -1615,7 +1627,6 @@
       <c r="H26" t="s">
         <v>17</v>
       </c>
-      <c r="I26"/>
       <c r="J26" t="s">
         <v>19</v>
       </c>
@@ -1623,9 +1634,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>44313.4608141782</v>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>44313.460814178201</v>
       </c>
       <c r="B27" t="s">
         <v>51</v>
@@ -1648,7 +1659,6 @@
       <c r="H27" t="s">
         <v>57</v>
       </c>
-      <c r="I27"/>
       <c r="J27" t="s">
         <v>19</v>
       </c>
@@ -1656,9 +1666,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>44313.4608557176</v>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>44313.460855717603</v>
       </c>
       <c r="B28" t="s">
         <v>11</v>
@@ -1691,9 +1701,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>44313.4608823264</v>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>44313.460882326399</v>
       </c>
       <c r="B29" t="s">
         <v>51</v>
@@ -1726,9 +1736,9 @@
         <v>99</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>44313.4608964815</v>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>44313.460896481498</v>
       </c>
       <c r="B30" t="s">
         <v>51</v>
@@ -1757,11 +1767,10 @@
       <c r="J30" t="s">
         <v>19</v>
       </c>
-      <c r="K30"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>44313.4609102778</v>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>44313.460910277798</v>
       </c>
       <c r="B31" t="s">
         <v>11</v>
@@ -1784,7 +1793,6 @@
       <c r="H31" t="s">
         <v>17</v>
       </c>
-      <c r="I31"/>
       <c r="J31" t="s">
         <v>19</v>
       </c>
@@ -1792,9 +1800,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>44313.4609240278</v>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>44313.460924027801</v>
       </c>
       <c r="B32" t="s">
         <v>11</v>
@@ -1827,9 +1835,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>44313.4609254398</v>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>44313.460925439802</v>
       </c>
       <c r="B33" t="s">
         <v>51</v>
@@ -1862,14 +1870,13 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>44313.4609431597</v>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>44313.460943159698</v>
       </c>
       <c r="B34" t="s">
         <v>11</v>
       </c>
-      <c r="C34"/>
       <c r="D34" t="s">
         <v>109</v>
       </c>
@@ -1895,8 +1902,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
         <v>44313.4609484838</v>
       </c>
       <c r="B35" t="s">
@@ -1923,16 +1930,14 @@
       <c r="I35" t="s">
         <v>26</v>
       </c>
-      <c r="J35"/>
       <c r="K35" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
         <v>44313.4610381366</v>
       </c>
-      <c r="B36"/>
       <c r="C36" t="s">
         <v>34</v>
       </c>
@@ -1961,9 +1966,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>44313.4610496412</v>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>44313.461049641199</v>
       </c>
       <c r="B37" t="s">
         <v>51</v>
@@ -1992,11 +1997,10 @@
       <c r="J37" t="s">
         <v>19</v>
       </c>
-      <c r="K37"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>44313.4610624884</v>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>44313.461062488401</v>
       </c>
       <c r="B38" t="s">
         <v>65</v>
@@ -2029,9 +2033,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>44313.4610740625</v>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>44313.461074062499</v>
       </c>
       <c r="B39" t="s">
         <v>11</v>
@@ -2039,7 +2043,6 @@
       <c r="C39" t="s">
         <v>28</v>
       </c>
-      <c r="D39"/>
       <c r="E39" t="s">
         <v>14</v>
       </c>
@@ -2062,9 +2065,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>44313.4610821181</v>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>44313.461082118098</v>
       </c>
       <c r="B40" t="s">
         <v>51</v>
@@ -2078,7 +2081,6 @@
       <c r="E40" t="s">
         <v>14</v>
       </c>
-      <c r="F40"/>
       <c r="G40" t="s">
         <v>80</v>
       </c>
@@ -2095,9 +2097,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>44313.4610994676</v>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
+        <v>44313.461099467597</v>
       </c>
       <c r="B41" t="s">
         <v>11</v>
@@ -2130,9 +2132,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>44313.4611264236</v>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
+        <v>44313.461126423601</v>
       </c>
       <c r="B42" t="s">
         <v>47</v>
@@ -2149,7 +2151,6 @@
       <c r="F42" t="s">
         <v>36</v>
       </c>
-      <c r="G42"/>
       <c r="H42" t="s">
         <v>50</v>
       </c>
@@ -2163,9 +2164,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>44313.4611265857</v>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
+        <v>44313.461126585702</v>
       </c>
       <c r="B43" t="s">
         <v>51</v>
@@ -2182,7 +2183,6 @@
       <c r="F43" t="s">
         <v>121</v>
       </c>
-      <c r="G43"/>
       <c r="H43" t="s">
         <v>57</v>
       </c>
@@ -2196,9 +2196,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>44313.4611317361</v>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A44" s="1">
+        <v>44313.461131736098</v>
       </c>
       <c r="B44" t="s">
         <v>11</v>
@@ -2231,9 +2231,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="1" t="n">
-        <v>44313.4611534143</v>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A45" s="1">
+        <v>44313.461153414297</v>
       </c>
       <c r="B45" t="s">
         <v>11</v>
@@ -2266,25 +2266,22 @@
         <v>20</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="1" t="n">
-        <v>44313.4611568171</v>
-      </c>
-      <c r="B46"/>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A46" s="1">
+        <v>44313.461156817102</v>
+      </c>
       <c r="C46" t="s">
         <v>21</v>
       </c>
       <c r="D46" t="s">
         <v>110</v>
       </c>
-      <c r="E46"/>
       <c r="F46" t="s">
         <v>36</v>
       </c>
       <c r="G46" t="s">
         <v>111</v>
       </c>
-      <c r="H46"/>
       <c r="I46" t="s">
         <v>18</v>
       </c>
@@ -2295,9 +2292,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="1" t="n">
-        <v>44313.4611578472</v>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A47" s="1">
+        <v>44313.461157847203</v>
       </c>
       <c r="B47" t="s">
         <v>11</v>
@@ -2330,9 +2327,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>44313.4611916435</v>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A48" s="1">
+        <v>44313.461191643502</v>
       </c>
       <c r="B48" t="s">
         <v>51</v>
@@ -2365,9 +2362,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="1" t="n">
-        <v>44313.4612161574</v>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A49" s="1">
+        <v>44313.461216157397</v>
       </c>
       <c r="B49" t="s">
         <v>51</v>
@@ -2400,9 +2397,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="1" t="n">
-        <v>44313.4612220023</v>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A50" s="1">
+        <v>44313.461222002297</v>
       </c>
       <c r="B50" t="s">
         <v>11</v>
@@ -2419,7 +2416,6 @@
       <c r="F50" t="s">
         <v>68</v>
       </c>
-      <c r="G50"/>
       <c r="H50" t="s">
         <v>57</v>
       </c>
@@ -2433,9 +2429,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="1" t="n">
-        <v>44313.4612273264</v>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A51" s="1">
+        <v>44313.461227326399</v>
       </c>
       <c r="B51" t="s">
         <v>11</v>
@@ -2452,7 +2448,6 @@
       <c r="F51" t="s">
         <v>68</v>
       </c>
-      <c r="G51"/>
       <c r="H51" t="s">
         <v>25</v>
       </c>
@@ -2468,6 +2463,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>